--- a/data/bodem_template.xlsx
+++ b/data/bodem_template.xlsx
@@ -4871,7 +4871,7 @@
     <t>Date generated</t>
   </si>
   <si>
-    <t>2024-07-24 09:00:00.647555</t>
+    <t>2024-07-24 09:03:31.753371</t>
   </si>
   <si>
     <t>version</t>
